--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260915.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260915.xlsx
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>71,026,216</t>
+          <t>1,841,915</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,841,915</t>
+          <t>71,026,216</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>113,681,316</t>
+          <t>17,508,396</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>17,508,396</t>
+          <t>113,681,316</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>26,239,489</t>
+          <t>247,419,216</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>247,419,216</t>
+          <t>26,239,489</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
